--- a/2_ResNet/DL_lecture/Evaluation result_Homework2.xlsx
+++ b/2_ResNet/DL_lecture/Evaluation result_Homework2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\김강민\가톨릭대학교\수업\2024-1\딥러닝\Homework3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kokyungwoo\PycharmProjects\DeepLearningStudy\2_ResNet\DL_Lecture\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96CC59E5-DDD7-45ED-A47C-BBACEFA147AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83265A2D-61C1-4792-93F8-55011D7E91ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="39">
   <si>
     <t>Batch_size</t>
   </si>
@@ -57,9 +57,6 @@
     <t>Validation dataset accuracy plot</t>
   </si>
   <si>
-    <t xml:space="preserve"> [결과 정리]</t>
-  </si>
-  <si>
     <t>Activation function</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -72,10 +69,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>add setting...</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Setting #3</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -141,6 +134,44 @@
   </si>
   <si>
     <t>Layer Norm</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>67.73 minutes</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Setting #1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>O (padding=4)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>61.73 minutes</t>
+  </si>
+  <si>
+    <t>66.19 minutes</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>#Setting3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>#Setting2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>76.51 minutes</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> [결과 정리]
+첫번째 세팅에서 90% 를 넘었음, 그래도 이후에 추가적인 비교를 위해 실험 진행 , 코드는 Setting 1 로 제출 Setting 1로 직접 다른 사진을 모아 추측한 결과 , 결과가 정확함을 확인함
+각 그래프마다 acc과 loss가 급격하게 줄어드는 구간이 있는데 이 구간은 32000 스텝 구간으로 learning rate decay로 learning rate가 줄어들는 구간이고 acc 과 loss가 빠르게 줄어드는 것으로 보임 -&gt; 기본적으로 acc 과 loss가 기대 이하일때는 learning rate를 줄이는게 빠르게 효과적임을 확인 할 수 있었다. 또한 그래프를 보아 이후 스텝에서는 val/loss가 늘어나는걸 보아
+early stopping을 적용하는게 효율성이 있을것으로 기대됨</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -148,7 +179,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -178,6 +209,20 @@
       <family val="2"/>
       <charset val="129"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -193,7 +238,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -333,13 +378,44 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -373,15 +449,48 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -399,6 +508,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -740,15 +852,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>174957</xdr:colOff>
+      <xdr:colOff>219542</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>273553</xdr:rowOff>
+      <xdr:rowOff>147904</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>272231</xdr:colOff>
+      <xdr:colOff>316816</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>207836</xdr:rowOff>
+      <xdr:rowOff>82187</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -766,8 +878,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="16434692" y="2402671"/>
-          <a:ext cx="1587657" cy="248047"/>
+          <a:off x="14912361" y="2251510"/>
+          <a:ext cx="1584795" cy="250432"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -838,6 +950,402 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>468966</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>74520</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1390650</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>166037</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="그림 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B3BE3336-D207-87EB-CAD3-8393D4ED4CF4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1126191" y="2798670"/>
+          <a:ext cx="2617134" cy="1034492"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>483536</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>258857</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>53313</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="그림 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD2EB806-BC00-2857-268C-1BFAD9A63FE4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1140761" y="3925982"/>
+          <a:ext cx="2640664" cy="1051756"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>366898</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>124579</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>361972</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>26927</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="그림 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F0EDE66E-AD6B-B827-9054-5D99D3E1DA3F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13470866" y="3492781"/>
+          <a:ext cx="1583925" cy="1799242"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>457551</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>99219</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>44295</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>33584</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="그림 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{43FCA6D3-C3A4-C83A-CA9E-A7CB46C53425}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15150370" y="3467421"/>
+          <a:ext cx="2415872" cy="1831259"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>119159</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>102045</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>359287</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>59981</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="그림 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B3FCCA44-5FA7-5326-FFAF-CD7B8AAA9519}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13223127" y="2521800"/>
+          <a:ext cx="6287490" cy="906383"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>678756</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>1601</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>1011390</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>299357</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="그림 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{16407925-DA98-5651-BCD6-1F9234D50CC2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9278470" y="2682208"/>
+          <a:ext cx="3149313" cy="1236649"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>722780</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>162485</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>1360714</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>291523</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="그림 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D573FCA6-4C5E-65B0-D1CB-D32F4CD0D98F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9322494" y="3781985"/>
+          <a:ext cx="3454613" cy="1380895"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1238253</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>142475</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>843644</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>146029</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="그림 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4DFA2A56-DD93-754D-B852-49528C98F16D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4993824" y="2823082"/>
+          <a:ext cx="2966356" cy="1255411"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>89066</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>103910</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>802822</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>262627</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="그림 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F812DBD-BC63-F94F-D7AF-8E9FCCF5638B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5205352" y="4036374"/>
+          <a:ext cx="2714006" cy="1097610"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -1140,55 +1648,55 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:P25"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <dimension ref="B1:P84"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.58203125" customWidth="1"/>
-    <col min="2" max="2" width="12.08203125" customWidth="1"/>
-    <col min="3" max="3" width="10.08203125" customWidth="1"/>
-    <col min="4" max="4" width="18.33203125" customWidth="1"/>
-    <col min="5" max="5" width="17.83203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.33203125" customWidth="1"/>
+    <col min="1" max="1" width="8.625" customWidth="1"/>
+    <col min="2" max="2" width="12.125" customWidth="1"/>
+    <col min="3" max="3" width="10.125" customWidth="1"/>
+    <col min="4" max="4" width="18.375" customWidth="1"/>
+    <col min="5" max="5" width="17.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.375" customWidth="1"/>
     <col min="8" max="8" width="19.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.58203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="22.25" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="22.25" customWidth="1"/>
-    <col min="12" max="12" width="20.83203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="19.5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17.58203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="21.375" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="10.25" bestFit="1" customWidth="1"/>
-    <col min="17" max="1027" width="8.58203125" customWidth="1"/>
+    <col min="17" max="1027" width="8.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:16" ht="17.5" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="2" spans="2:16" ht="30.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B2" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="11"/>
-      <c r="L2" s="11"/>
-      <c r="M2" s="11"/>
-      <c r="N2" s="11"/>
-      <c r="O2" s="11"/>
-      <c r="P2" s="11"/>
-    </row>
-    <row r="3" spans="2:16" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:16" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="23"/>
+      <c r="M2" s="23"/>
+      <c r="N2" s="23"/>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+    </row>
+    <row r="3" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B3" s="1"/>
       <c r="C3" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>1</v>
@@ -1197,25 +1705,25 @@
         <v>2</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>3</v>
@@ -1227,48 +1735,54 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:16" x14ac:dyDescent="0.45">
-      <c r="B4" s="7" t="s">
+    <row r="4" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B4" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="12">
         <v>128</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" s="4">
-        <v>0.01</v>
-      </c>
-      <c r="G4" s="4">
+      <c r="E4" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="G4" s="12">
         <v>200</v>
       </c>
-      <c r="H4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="M4" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="N4" s="4"/>
-      <c r="O4" s="4"/>
-      <c r="P4" s="5"/>
-    </row>
-    <row r="5" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="H4" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="J4" s="13">
+        <v>1E-4</v>
+      </c>
+      <c r="K4" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="L4" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="M4" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="N4" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="O4" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="P4" s="14">
+        <v>0.92059999999999997</v>
+      </c>
+    </row>
+    <row r="5" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
         <v>8</v>
       </c>
@@ -1279,7 +1793,7 @@
         <v>7</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F5" s="4">
         <v>0.01</v>
@@ -1288,30 +1802,36 @@
         <v>200</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J5" s="4">
         <v>1E-4</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="N5" s="4"/>
-      <c r="O5" s="4"/>
-      <c r="P5" s="5"/>
-    </row>
-    <row r="6" spans="2:16" x14ac:dyDescent="0.45">
+        <v>11</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="O5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="P5" s="5">
+        <v>86.06</v>
+      </c>
+    </row>
+    <row r="6" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B6" s="7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C6" s="4">
         <v>128</v>
@@ -1320,7 +1840,7 @@
         <v>7</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F6" s="4">
         <v>0.01</v>
@@ -1329,30 +1849,36 @@
         <v>200</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J6" s="4">
         <v>1E-4</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="N6" s="4"/>
-      <c r="O6" s="4"/>
-      <c r="P6" s="5"/>
-    </row>
-    <row r="7" spans="2:16" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+      <c r="N6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="O6" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="P6" s="5">
+        <v>92.18</v>
+      </c>
+    </row>
+    <row r="7" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B7" s="7" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C7" s="4">
         <v>128</v>
@@ -1361,7 +1887,7 @@
         <v>7</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F7" s="4">
         <v>0.01</v>
@@ -1370,31 +1896,35 @@
         <v>200</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J7" s="4">
         <v>1E-4</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="N7" s="4"/>
-      <c r="O7" s="4"/>
-      <c r="P7" s="5"/>
-    </row>
-    <row r="8" spans="2:16" x14ac:dyDescent="0.45">
-      <c r="B8" s="8" t="s">
-        <v>14</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="N7" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="O7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="P7" s="5">
+        <v>87.58</v>
+      </c>
+    </row>
+    <row r="8" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B8" s="8"/>
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
@@ -1410,293 +1940,308 @@
       <c r="O8" s="9"/>
       <c r="P8" s="10"/>
     </row>
-    <row r="9" spans="2:16" x14ac:dyDescent="0.45">
-      <c r="B9" s="12" t="s">
+    <row r="9" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B9" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="24"/>
       <c r="P9" s="6"/>
     </row>
-    <row r="10" spans="2:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B10" s="14"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15"/>
-      <c r="I10" s="15"/>
-      <c r="J10" s="15"/>
-      <c r="K10" s="16"/>
-      <c r="L10" s="14"/>
-      <c r="M10" s="15"/>
-      <c r="N10" s="15"/>
-      <c r="O10" s="15"/>
-      <c r="P10" s="16"/>
-    </row>
-    <row r="11" spans="2:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B11" s="14"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15"/>
-      <c r="I11" s="15"/>
-      <c r="J11" s="15"/>
-      <c r="K11" s="16"/>
-      <c r="L11" s="14"/>
-      <c r="M11" s="15"/>
-      <c r="N11" s="15"/>
-      <c r="O11" s="15"/>
-      <c r="P11" s="16"/>
-    </row>
-    <row r="12" spans="2:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B12" s="14"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="15"/>
-      <c r="I12" s="15"/>
-      <c r="J12" s="15"/>
-      <c r="K12" s="16"/>
-      <c r="L12" s="14"/>
-      <c r="M12" s="15"/>
-      <c r="N12" s="15"/>
-      <c r="O12" s="15"/>
-      <c r="P12" s="16"/>
-    </row>
-    <row r="13" spans="2:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B13" s="14"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15"/>
-      <c r="I13" s="15"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="16"/>
-      <c r="L13" s="14"/>
-      <c r="M13" s="15"/>
-      <c r="N13" s="15"/>
-      <c r="O13" s="15"/>
-      <c r="P13" s="16"/>
-    </row>
-    <row r="14" spans="2:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B14" s="14"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="15"/>
-      <c r="I14" s="15"/>
-      <c r="J14" s="15"/>
-      <c r="K14" s="16"/>
-      <c r="L14" s="14"/>
-      <c r="M14" s="15"/>
-      <c r="N14" s="15"/>
-      <c r="O14" s="15"/>
-      <c r="P14" s="16"/>
-    </row>
-    <row r="15" spans="2:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B15" s="14"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="15"/>
-      <c r="I15" s="15"/>
-      <c r="J15" s="15"/>
-      <c r="K15" s="16"/>
-      <c r="L15" s="14"/>
-      <c r="M15" s="15"/>
-      <c r="N15" s="15"/>
-      <c r="O15" s="15"/>
-      <c r="P15" s="16"/>
-    </row>
-    <row r="16" spans="2:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B16" s="14"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="15"/>
-      <c r="I16" s="15"/>
-      <c r="J16" s="15"/>
-      <c r="K16" s="16"/>
-      <c r="L16" s="14"/>
-      <c r="M16" s="15"/>
-      <c r="N16" s="15"/>
-      <c r="O16" s="15"/>
-      <c r="P16" s="16"/>
-    </row>
-    <row r="17" spans="2:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B17" s="14"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="15"/>
-      <c r="H17" s="15"/>
-      <c r="I17" s="15"/>
-      <c r="J17" s="15"/>
-      <c r="K17" s="16"/>
-      <c r="L17" s="14"/>
-      <c r="M17" s="15"/>
-      <c r="N17" s="15"/>
-      <c r="O17" s="15"/>
-      <c r="P17" s="16"/>
-    </row>
-    <row r="18" spans="2:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B18" s="14"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="15"/>
-      <c r="I18" s="15"/>
-      <c r="J18" s="15"/>
-      <c r="K18" s="16"/>
-      <c r="L18" s="14"/>
-      <c r="M18" s="15"/>
-      <c r="N18" s="15"/>
-      <c r="O18" s="15"/>
-      <c r="P18" s="16"/>
-    </row>
-    <row r="19" spans="2:16" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B19" s="17"/>
-      <c r="C19" s="18"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="18"/>
-      <c r="I19" s="18"/>
-      <c r="J19" s="18"/>
-      <c r="K19" s="19"/>
-      <c r="L19" s="17"/>
-      <c r="M19" s="18"/>
-      <c r="N19" s="18"/>
-      <c r="O19" s="18"/>
-      <c r="P19" s="19"/>
-    </row>
-    <row r="20" spans="2:16" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B20" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="13"/>
-      <c r="J20" s="13"/>
-      <c r="K20" s="13"/>
-      <c r="L20" s="13"/>
-      <c r="M20" s="13"/>
-      <c r="N20" s="13"/>
-      <c r="O20" s="13"/>
-      <c r="P20" s="13"/>
-    </row>
-    <row r="21" spans="2:16" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="13"/>
-      <c r="J21" s="13"/>
-      <c r="K21" s="13"/>
-      <c r="L21" s="13"/>
-      <c r="M21" s="13"/>
-      <c r="N21" s="13"/>
-      <c r="O21" s="13"/>
-      <c r="P21" s="13"/>
-    </row>
-    <row r="22" spans="2:16" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B22" s="13"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="13"/>
-      <c r="I22" s="13"/>
-      <c r="J22" s="13"/>
-      <c r="K22" s="13"/>
-      <c r="L22" s="13"/>
-      <c r="M22" s="13"/>
-      <c r="N22" s="13"/>
-      <c r="O22" s="13"/>
-      <c r="P22" s="13"/>
-    </row>
-    <row r="23" spans="2:16" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="13"/>
-      <c r="I23" s="13"/>
-      <c r="J23" s="13"/>
-      <c r="K23" s="13"/>
-      <c r="L23" s="13"/>
-      <c r="M23" s="13"/>
-      <c r="N23" s="13"/>
-      <c r="O23" s="13"/>
-      <c r="P23" s="13"/>
-    </row>
-    <row r="24" spans="2:16" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="13"/>
-      <c r="I24" s="13"/>
-      <c r="J24" s="13"/>
-      <c r="K24" s="13"/>
-      <c r="L24" s="13"/>
-      <c r="M24" s="13"/>
-      <c r="N24" s="13"/>
-      <c r="O24" s="13"/>
-      <c r="P24" s="13"/>
-    </row>
-    <row r="25" spans="2:16" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B25" s="13"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="13"/>
-      <c r="H25" s="13"/>
-      <c r="I25" s="13"/>
-      <c r="J25" s="13"/>
-      <c r="K25" s="13"/>
-      <c r="L25" s="13"/>
-      <c r="M25" s="13"/>
-      <c r="N25" s="13"/>
-      <c r="O25" s="13"/>
-      <c r="P25" s="13"/>
+    <row r="10" spans="2:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="25"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="26"/>
+      <c r="I10" s="26"/>
+      <c r="J10" s="26"/>
+      <c r="K10" s="27"/>
+      <c r="L10" s="25"/>
+      <c r="M10" s="26"/>
+      <c r="N10" s="26"/>
+      <c r="O10" s="26"/>
+      <c r="P10" s="27"/>
+    </row>
+    <row r="11" spans="2:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="25"/>
+      <c r="C11" s="26"/>
+      <c r="D11" s="26"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="26"/>
+      <c r="G11" s="26"/>
+      <c r="H11" s="26"/>
+      <c r="I11" s="26"/>
+      <c r="J11" s="26"/>
+      <c r="K11" s="27"/>
+      <c r="L11" s="25"/>
+      <c r="M11" s="26"/>
+      <c r="N11" s="26"/>
+      <c r="O11" s="26"/>
+      <c r="P11" s="27"/>
+    </row>
+    <row r="12" spans="2:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="25"/>
+      <c r="C12" s="26"/>
+      <c r="D12" s="26"/>
+      <c r="E12" s="26"/>
+      <c r="F12" s="26"/>
+      <c r="G12" s="26"/>
+      <c r="H12" s="26"/>
+      <c r="I12" s="26"/>
+      <c r="J12" s="26"/>
+      <c r="K12" s="27"/>
+      <c r="L12" s="25"/>
+      <c r="M12" s="26"/>
+      <c r="N12" s="26"/>
+      <c r="O12" s="26"/>
+      <c r="P12" s="27"/>
+    </row>
+    <row r="13" spans="2:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="25"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="26"/>
+      <c r="G13" s="26"/>
+      <c r="H13" s="26"/>
+      <c r="I13" s="26"/>
+      <c r="J13" s="26"/>
+      <c r="K13" s="27"/>
+      <c r="L13" s="25"/>
+      <c r="M13" s="26"/>
+      <c r="N13" s="26"/>
+      <c r="O13" s="26"/>
+      <c r="P13" s="27"/>
+    </row>
+    <row r="14" spans="2:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="25"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="26"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="26"/>
+      <c r="G14" s="26"/>
+      <c r="H14" s="26"/>
+      <c r="I14" s="26"/>
+      <c r="J14" s="26"/>
+      <c r="K14" s="27"/>
+      <c r="L14" s="25"/>
+      <c r="M14" s="26"/>
+      <c r="N14" s="26"/>
+      <c r="O14" s="26"/>
+      <c r="P14" s="27"/>
+    </row>
+    <row r="15" spans="2:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="25"/>
+      <c r="C15" s="26"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="26"/>
+      <c r="F15" s="26"/>
+      <c r="G15" s="26"/>
+      <c r="H15" s="26"/>
+      <c r="I15" s="26"/>
+      <c r="J15" s="26"/>
+      <c r="K15" s="27"/>
+      <c r="L15" s="25"/>
+      <c r="M15" s="26"/>
+      <c r="N15" s="26"/>
+      <c r="O15" s="26"/>
+      <c r="P15" s="27"/>
+    </row>
+    <row r="16" spans="2:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="25"/>
+      <c r="C16" s="26"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="26"/>
+      <c r="H16" s="26"/>
+      <c r="I16" s="26"/>
+      <c r="J16" s="26"/>
+      <c r="K16" s="27"/>
+      <c r="L16" s="25"/>
+      <c r="M16" s="26"/>
+      <c r="N16" s="26"/>
+      <c r="O16" s="26"/>
+      <c r="P16" s="27"/>
+    </row>
+    <row r="17" spans="2:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="25"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="26"/>
+      <c r="G17" s="26"/>
+      <c r="H17" s="26"/>
+      <c r="I17" s="26"/>
+      <c r="J17" s="26"/>
+      <c r="K17" s="27"/>
+      <c r="L17" s="25"/>
+      <c r="M17" s="26"/>
+      <c r="N17" s="26"/>
+      <c r="O17" s="26"/>
+      <c r="P17" s="27"/>
+    </row>
+    <row r="18" spans="2:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="25"/>
+      <c r="C18" s="26"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="26"/>
+      <c r="G18" s="26"/>
+      <c r="H18" s="26"/>
+      <c r="I18" s="26"/>
+      <c r="J18" s="26"/>
+      <c r="K18" s="27"/>
+      <c r="L18" s="25"/>
+      <c r="M18" s="26"/>
+      <c r="N18" s="26"/>
+      <c r="O18" s="26"/>
+      <c r="P18" s="27"/>
+    </row>
+    <row r="19" spans="2:16" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B19" s="28"/>
+      <c r="C19" s="29"/>
+      <c r="D19" s="29"/>
+      <c r="E19" s="29"/>
+      <c r="F19" s="29"/>
+      <c r="G19" s="29"/>
+      <c r="H19" s="29"/>
+      <c r="I19" s="29"/>
+      <c r="J19" s="29"/>
+      <c r="K19" s="30"/>
+      <c r="L19" s="28"/>
+      <c r="M19" s="29"/>
+      <c r="N19" s="29"/>
+      <c r="O19" s="29"/>
+      <c r="P19" s="30"/>
+    </row>
+    <row r="20" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B20" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" s="15"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="15"/>
+      <c r="I20" s="15"/>
+      <c r="J20" s="15"/>
+      <c r="K20" s="15"/>
+      <c r="L20" s="15"/>
+      <c r="M20" s="15"/>
+      <c r="N20" s="15"/>
+      <c r="O20" s="15"/>
+      <c r="P20" s="16"/>
+    </row>
+    <row r="21" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B21" s="17"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="18"/>
+      <c r="J21" s="18"/>
+      <c r="K21" s="18"/>
+      <c r="L21" s="18"/>
+      <c r="M21" s="18"/>
+      <c r="N21" s="18"/>
+      <c r="O21" s="18"/>
+      <c r="P21" s="19"/>
+    </row>
+    <row r="22" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B22" s="17"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
+      <c r="I22" s="18"/>
+      <c r="J22" s="18"/>
+      <c r="K22" s="18"/>
+      <c r="L22" s="18"/>
+      <c r="M22" s="18"/>
+      <c r="N22" s="18"/>
+      <c r="O22" s="18"/>
+      <c r="P22" s="19"/>
+    </row>
+    <row r="23" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B23" s="17"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="18"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="18"/>
+      <c r="J23" s="18"/>
+      <c r="K23" s="18"/>
+      <c r="L23" s="18"/>
+      <c r="M23" s="18"/>
+      <c r="N23" s="18"/>
+      <c r="O23" s="18"/>
+      <c r="P23" s="19"/>
+    </row>
+    <row r="24" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B24" s="17"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="18"/>
+      <c r="I24" s="18"/>
+      <c r="J24" s="18"/>
+      <c r="K24" s="18"/>
+      <c r="L24" s="18"/>
+      <c r="M24" s="18"/>
+      <c r="N24" s="18"/>
+      <c r="O24" s="18"/>
+      <c r="P24" s="19"/>
+    </row>
+    <row r="25" spans="2:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B25" s="20"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
+      <c r="G25" s="21"/>
+      <c r="H25" s="21"/>
+      <c r="I25" s="21"/>
+      <c r="J25" s="21"/>
+      <c r="K25" s="21"/>
+      <c r="L25" s="21"/>
+      <c r="M25" s="21"/>
+      <c r="N25" s="21"/>
+      <c r="O25" s="21"/>
+      <c r="P25" s="22"/>
+    </row>
+    <row r="34" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D34" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="75" spans="13:13" x14ac:dyDescent="0.3">
+      <c r="M75" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="84" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D84" t="s">
+        <v>35</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="B20:P25"/>
     <mergeCell ref="B2:P2"/>
     <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B20:P25"/>
     <mergeCell ref="B10:K19"/>
     <mergeCell ref="L10:P19"/>
   </mergeCells>
